--- a/public/exports-with-coowners/19438414.xlsx
+++ b/public/exports-with-coowners/19438414.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024939</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">

--- a/public/exports-with-coowners/19438414.xlsx
+++ b/public/exports-with-coowners/19438414.xlsx
@@ -2539,7 +2539,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024939</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5179,12 +5179,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5554,12 +5554,12 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5704,12 +5704,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5779,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6004,12 +6004,12 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6229,12 +6229,12 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6304,12 +6304,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports-with-coowners/19438414.xlsx
+++ b/public/exports-with-coowners/19438414.xlsx
@@ -2539,7 +2539,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6904,12 +6904,12 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6979,12 +6979,12 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -7054,12 +7054,12 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -7129,12 +7129,12 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -7204,12 +7204,12 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
